--- a/Perbandingan NAS dan PC untuk shate fpler.xlsx
+++ b/Perbandingan NAS dan PC untuk shate fpler.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Perbandingan NAS dan PC untuk share folder</t>
   </si>
@@ -112,6 +112,16 @@
   </si>
   <si>
     <t>Linux/TrueNAS/Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kesimpulan : </t>
+  </si>
+  <si>
+    <t>Kalau fokus utama adalah kemudahan restore dan proteksi dari user error → NAS lebih unggul.
+Kalau fokus utama adalah kontrol akses detail dan integrasi dengan sistem lain → PC server lebih tepat.</t>
+  </si>
+  <si>
+    <t>Kemudahan Restore File kemungkinan lebih critical daripada pengaturan akses file yang masih bisa diatur di level folder -&gt; NAS lebih unggul</t>
   </si>
 </sst>
 </file>
@@ -135,7 +145,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -154,6 +164,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -219,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -234,6 +256,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -535,7 +562,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I19"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="95.5703125" customWidth="1"/>
@@ -556,10 +586,10 @@
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
     </row>
@@ -621,79 +651,96 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" t="s">
-        <v>31</v>
-      </c>
+      <c r="A14" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="80" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
